--- a/02_加值成品/八上/八上5-4_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上5-4_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上5-4 熱與物質變化　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國二上學期 八上5-4 熱與物質變化　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>物質受熱體積如何？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>膨脹</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>暫時不變</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>熱脹變形</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>氣體</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>熱脹</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>熱脹冷縮幅度最大的是？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>氣體</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>膨脹</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>放熱</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>汽化</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>分子自由</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>固→液的物態變化是？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>熔化</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>凝華</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>膨脹</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>汽化</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>吸熱</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>液→氣的物態變化是？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>汽化</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>凝結</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>暫時不變</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>膨脹</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>吸熱</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>氣→液的物態變化是？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>潛熱</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>昇華</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>熱脹變形</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>凝結</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>放熱</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>物態變化時溫度如何？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>凝華</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>暫時不變</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>放熱</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>潛熱</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="34" customHeight="1">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>潛熱</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>固體直接變氣體是？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>昇華</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>凝結</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>熱脹變形</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>熔化</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>如乾冰</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>鐵軌留縫是為了防？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>熱脹變形</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>物態變化</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>昇華</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>能</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>伸縮</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>水沸騰變成水蒸氣屬？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>汽化</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>放熱</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>暫時不變</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>熔化</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>液→氣</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>鋼軌夏天膨脹是因為？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>暫時不變</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>潛熱</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>熱脹冷縮</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>膨脹</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>熱脹</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上5-4 熱與物質變化　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國二上學期 八上5-4 熱與物質變化　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>加熱曲線的水平段代表？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>汽化</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>物態變化</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>凝結</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>吸熱</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>溫度不變</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>熔化過程吸熱或放熱？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>熱脹冷縮</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>汽化</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>氣體</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>吸熱</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>需能量</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>凝固過程吸熱或放熱？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>膨脹</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>不變</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>氣體</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>放熱</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>釋能量</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>冰在0℃熔化溫度變嗎？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>不變</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>能</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>氣體</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>膨脹</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>潛熱</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>蒸發能在低於沸點發生嗎？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>凝華</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>熔化</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>能</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>膨脹</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>任何溫度</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>水沸騰時溫度維持在？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>蒸發加快帶走水分</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>沸點(100℃)</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>用於改變物態(潛熱)</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>該物態變化吸放熱越多</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>平段</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>氣→固直接變化是？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>昇華</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>凝華</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>氣體</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>物態變化</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>放熱</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>溫度計利用液體的？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>氣體</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>汽化</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>熱脹冷縮</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>放熱</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>測溫</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>物態變化時吸放的熱稱？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>熱脹冷縮</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>潛熱</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>暫時不變</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>吸熱</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>潛熱</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>液→固的物態變化是？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>能</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>暫時不變</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>膨脹</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>凝固</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>放熱</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上5-4 熱與物質變化　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國二上學期 八上5-4 熱與物質變化　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>冰水混合物加熱到沸騰溫度如何變化？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>汗蒸發吸收潛熱帶走體熱</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>受熱膨脹佔用縫隙</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>該物態變化吸放熱越多</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>升到0℃平(熔)→升溫→100℃平(沸)</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>兩平段</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>為何流汗能散熱？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>該物態變化吸放熱越多</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>汗蒸發吸收潛熱帶走體熱</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>蒸發加快帶走水分</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>液體熱脹冷縮體積隨溫變</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>汽化吸熱</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>固體受熱膨脹幅度為何小於氣體？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>液體熱脹冷縮體積隨溫變</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>粒子束縛強活動空間小</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>升到0℃平(熔)→升溫→100℃平(沸)</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>受熱膨脹佔用縫隙</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>結構</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>橋樑伸縮縫夏天變窄因為？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>受熱膨脹佔用縫隙</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>冰熔化吸收身體熱量</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>沸點(100℃)</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>汗蒸發吸收潛熱帶走體熱</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>熱脹</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>冰敷為何能退燒？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>升到0℃平(熔)→升溫→100℃平(沸)</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>冰熔化吸收身體熱量</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>粒子束縛強活動空間小</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>液體熱脹冷縮體積隨溫變</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>潛熱</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>加熱曲線平段越長代表？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>該物態變化吸放熱越多</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>受熱膨脹佔用縫隙</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>液體熱脹冷縮體積隨溫變</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>汗蒸發吸收潛熱帶走體熱</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>潛熱量</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>乾冰放空氣中冒白煙是？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>昇華並使水氣凝結</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>該物態變化吸放熱越多</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>沸點(100℃)</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>汗蒸發吸收潛熱帶走體熱</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>複合</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>溫度不變仍加熱,能量去哪？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>液體熱脹冷縮體積隨溫變</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>升到0℃平(熔)→升溫→100℃平(沸)</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>汗蒸發吸收潛熱帶走體熱</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>用於改變物態(潛熱)</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>守恆</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>為何濕衣晾通風處乾得快？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>該物態變化吸放熱越多</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>粒子束縛強活動空間小</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>冰熔化吸收身體熱量</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>蒸發加快帶走水分</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>蒸發</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>溫度計液柱能指示溫度的原理？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>液體熱脹冷縮體積隨溫變</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>汗蒸發吸收潛熱帶走體熱</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>受熱膨脹佔用縫隙</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>沸點(100℃)</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>熱脹</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/八上/八上5-4_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上5-4_三種難度測驗卷.xlsx
@@ -1530,7 +1530,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>升到0℃平(熔)→升溫→100℃平(沸)</t>
+          <t>維持0℃(熔化)→升溫→100℃平(沸)</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>升到0℃平(熔)→升溫→100℃平(沸)</t>
+          <t>維持0℃(熔化)→升溫→100℃平(沸)</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>升到0℃平(熔)→升溫→100℃平(沸)</t>
+          <t>維持0℃(熔化)→升溫→100℃平(沸)</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>升到0℃平(熔)→升溫→100℃平(沸)</t>
+          <t>維持0℃(熔化)→升溫→100℃平(沸)</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">

--- a/02_加值成品/八上/八上5-4_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上5-4_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>熱脹</t>
+          <t>熱脹：物質受熱後粒子運動變劇烈、間距通常變大，整體體積會膨脹</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>分子自由</t>
+          <t>分子自由：氣體分子間距離大、幾乎不受束縛，受熱膨脹的幅度比固體、液體明顯大很多</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>吸熱</t>
+          <t>吸熱：固體受熱吸收能量後變成液體，這個過程稱為熔化，需要吸收熱量(潛熱)</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>吸熱</t>
+          <t>吸熱：液體受熱吸收能量後變成氣體，這個過程稱為汽化，需要吸收熱量(潛熱)</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>放熱</t>
+          <t>放熱：氣體遇冷失去能量變成液體，這個過程稱為凝結，會釋放出熱量</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>潛熱</t>
+          <t>潛熱：物質在改變狀態的過程中，雖然持續吸熱或放熱，但溫度會暫時維持不變，這些熱量稱為潛熱</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>如乾冰</t>
+          <t>如乾冰：固態物質不經過液態，直接變成氣態的過程稱為昇華，乾冰(固態二氧化碳)就是常見的例子</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>伸縮</t>
+          <t>伸縮：鐵軌熱脹冷縮明顯，接縫間預留空隙，可以讓鐵軌在夏天受熱膨脹時有空間伸展，避免因擠壓而彎曲變形</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>液→氣</t>
+          <t>液→氣：物質從液態變成氣態的過程稱為汽化，水沸騰變成水蒸氣就是汽化現象</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>熱脹</t>
+          <t>熱脹：物質溫度升高時體積通常會膨脹，鋼軌在夏天氣溫高時因熱脹冷縮的原理而膨脹伸長</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>溫度不變</t>
+          <t>溫度不變：加熱曲線圖上溫度保持水平不變的那一段，代表物質正在進行物態變化(如熔化或沸騰)，吸收的熱量都用來改變狀態而非升溫</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>需能量</t>
+          <t>需能量：固體要變成液體，需要吸收熱量(潛熱)來克服粒子間的束縛力，所以熔化是吸熱過程</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>釋能量</t>
+          <t>釋能量：液體要變成固體，粒子排列變得更規則緊密，多餘的能量會以熱的形式釋放出來，所以凝固是放熱過程</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>潛熱</t>
+          <t>潛熱：冰在熔化過程中持續吸收熱量，但這些熱量用來把固態的冰轉變成液態的水(潛熱)，溫度會維持在0℃不變，直到完全熔化</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>任何溫度</t>
+          <t>任何溫度：蒸發是液體表面的分子隨時都可能獲得足夠能量逃逸成氣體，這種現象在任何溫度下都可能發生，不一定要達到沸點</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>平段</t>
+          <t>平段：水沸騰的過程中持續吸熱進行汽化，溫度會維持在沸點(1大氣壓下為100℃)不變，這是加熱曲線上的水平段</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>放熱</t>
+          <t>放熱：氣態物質不經過液態，直接變成固態的過程稱為凝華，這個過程會釋放出熱量</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>測溫</t>
+          <t>測溫：溫度計內的液體受熱膨脹、變冷收縮，液柱高度隨溫度改變，利用這種熱脹冷縮的特性來指示溫度</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>潛熱</t>
+          <t>潛熱：物質在改變狀態(如熔化、汽化)的過程中，溫度不變但會吸收或釋放熱量，這種熱稱為潛熱</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>放熱</t>
+          <t>放熱：物質從液態變成固態的過程稱為凝固，凝固過程會釋放熱量</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>兩平段</t>
+          <t>兩平段：冰水混合物本身就處於0℃的熔化平衡狀態，持續加熱時溫度先維持在0℃直到冰完全熔化，接著溫度開始上升，到達100℃後又維持平段進行沸騰(汽化)</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>汽化吸熱</t>
+          <t>汽化吸熱：汗水從液態蒸發成氣態時需要吸收大量熱量(汽化潛熱)，這些熱量取自皮膚表面，因此能有效幫助身體散熱降溫</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>結構</t>
+          <t>結構：固體粒子排列緊密、彼此有很強的束縛力，受熱時活動空間有限，膨脹幅度自然比幾乎不受束縛、能自由擴散的氣體小很多</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>熱脹</t>
+          <t>熱脹：夏天氣溫高，橋樑材料因熱脹冷縮而膨脹伸長，原本預留的伸縮縫隙因此被佔用而變窄</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>潛熱</t>
+          <t>潛熱：冰塊熔化成水的過程需要吸收大量熱量(熔化潛熱)，這些熱量從發燒的身體皮膚吸取，因此能幫助降低體溫</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>潛熱量</t>
+          <t>潛熱量：加熱曲線上水平段的長度反映了完成該物態變化所需吸收(或釋放)的總熱量，平段越長代表需要的潛熱量越多</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>複合</t>
+          <t>複合：乾冰昇華直接從固態變成低溫的二氧化碳氣體，使周圍空氣溫度驟降，讓空氣中的水氣遇冷凝結成看得見的白色小水滴(煙霧)，這是兩種現象同時發生的複合過程</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>守恆</t>
+          <t>守恆：物態變化過程中持續加熱但溫度不變，這些吸收進來的能量並沒有消失，而是全部用來克服粒子間的束縛力、改變物質的狀態，這些能量稱為潛熱，符合能量守恆</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>蒸發</t>
+          <t>蒸發：通風處空氣流動快，能不斷把衣服表面蒸發出來的水氣帶走，維持較低的濕度，讓水分持續加速蒸發，衣服因此乾得比較快</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>熱脹</t>
+          <t>熱脹：溫度計內的液體(如水銀、酒精)溫度升高時體積膨脹、液柱上升，溫度降低時體積收縮、液柱下降，靠這種熱脹冷縮的特性來指示溫度</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/八上/八上5-4_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上5-4_三種難度測驗卷.xlsx
@@ -763,7 +763,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>凝華</t>
+          <t>膨脹</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -773,12 +773,12 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>放熱</t>
+          <t>熔化</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>潛熱</t>
+          <t>氣體</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -1164,17 +1164,17 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>潛熱</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>物態變化</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
           <t>能</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>氣體</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>膨脹</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
